--- a/AAII_Financials/Yearly/KBR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KBR_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>KBR</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6956000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6564000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7339000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5767000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5639000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4913000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4171000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4268000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5096000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6366000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7214000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7770000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9103000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5979000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5736000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13066000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10202000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4986000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8786000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7561000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4156000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4771000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6431000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6797000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7252000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8463000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>977000</v>
+      </c>
+      <c r="E10" s="3">
         <v>828000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-5727000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-4435000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>653000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-3873000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-3390000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>112000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>325000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-65000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>417000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>518000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>640000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>14000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>420000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-101000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>39000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>70000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>660000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>360000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6578000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6221000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7108000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5710000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5277000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4445000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3907000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4240000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4786000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7160000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6906000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7471000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8516000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>378000</v>
+      </c>
+      <c r="E18" s="3">
         <v>343000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>231000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>362000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>468000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>264000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>310000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-794000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>308000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>299000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>587000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,115 +1178,122 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E20" s="3">
         <v>28000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>17000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-11000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>372000</v>
+      </c>
+      <c r="E21" s="3">
         <v>508000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>372000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>173000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>433000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>525000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>316000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>78000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>351000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-705000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>368000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>353000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>643000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E22" s="3">
         <v>87000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>80000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>72000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>99000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>21000</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="E23" s="3">
         <v>284000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>146000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>268000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>396000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>247000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>33000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>312000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-777000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>300000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>288000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>572000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E24" s="3">
         <v>92000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>111000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>28000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>86000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-29000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>84000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>86000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>421000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>129000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>86000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-261000</v>
+      </c>
+      <c r="E26" s="3">
         <v>192000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>35000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-42000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>209000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>310000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>276000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-51000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>226000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1198000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>171000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>202000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>540000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E27" s="3">
         <v>189000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-63000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>202000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>281000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>268000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-61000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>203000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1262000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>75000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>143000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>478000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,11 +1604,11 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3">
         <v>164000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-17000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>11000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E33" s="3">
         <v>189000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-63000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>202000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>281000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>432000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-61000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>203000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1262000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>75000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>143000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>478000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E35" s="3">
         <v>189000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-63000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>202000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>281000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>432000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-61000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>203000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1262000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>75000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>143000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>478000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E41" s="3">
         <v>389000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>370000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>436000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>712000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>739000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>439000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>536000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>883000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>970000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1106000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1053000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>966000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,51 +2073,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1191000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1218000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1656000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1099000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1190000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1141000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>904000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1408000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>861000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1364000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1543000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1790000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1654000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2054,233 +2149,251 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
         <v>5000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13000</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E45" s="3">
         <v>140000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>126000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>99000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>109000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>187000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>82000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>103000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>204000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>202000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>523000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1065000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>815000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1651000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1747000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2152000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1634000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2011000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1959000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1425000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2047000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1844000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2454000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2925000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3444000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3435000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E47" s="3">
         <v>217000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>606000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>911000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>909000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>822000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>488000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>500000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>807000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>721000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>784000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>735000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>503000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E48" s="3">
         <v>346000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>294000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>284000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>305000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>597000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>130000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>145000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>690000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>247000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1227000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>390000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>384000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2727000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2732000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2768000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2444000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1760000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2297000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1207000</v>
       </c>
       <c r="J49" s="3">
         <v>1207000</v>
       </c>
       <c r="K49" s="3">
+        <v>1207000</v>
+      </c>
+      <c r="L49" s="3">
         <v>429000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>365000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>942000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>878000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1064000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>604000</v>
+      </c>
+      <c r="E52" s="3">
         <v>524000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>384000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>432000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>379000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>369000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>424000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>245000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>233000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>291000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>457000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>320000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>280000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5565000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5566000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6204000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5705000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5364000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5052000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3674000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4144000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3412000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4078000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5438000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5767000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5666000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,76 +2654,80 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>593000</v>
+      </c>
+      <c r="E57" s="3">
         <v>637000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1026000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>574000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>572000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>546000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>350000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>535000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>438000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>742000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>747000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>756000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>761000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E58" s="3">
         <v>373000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>25000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>38000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>32000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>10000</v>
       </c>
       <c r="L58" s="3">
         <v>10000</v>
@@ -2606,179 +2739,194 @@
         <v>10000</v>
       </c>
       <c r="O58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="P58" s="3">
         <v>11000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>937000</v>
+      </c>
+      <c r="E59" s="3">
         <v>811000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>889000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>864000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>891000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1028000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>711000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1015000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1227000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1226000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1559000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2112000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1506000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1572000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1821000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1875000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1455000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1501000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1419000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1071000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1559000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1393000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1978000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1907000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2184000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2277000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1811000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1386000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1875000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1586000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1190000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1243000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>498000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>684000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>63000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>78000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>84000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>88000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>788000</v>
+      </c>
+      <c r="E62" s="3">
         <v>727000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>977000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1055000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>816000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>672000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>884000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1156000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>916000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1102000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1014000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1072000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>867000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4182000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3946000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4535000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4125000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3521000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3354000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2445000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3387000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2347000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3136000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2975000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3225000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3171000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1072000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1410000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1287000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1305000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1441000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1235000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>877000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>488000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2021000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1754000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1748000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1709000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1607000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1383000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1620000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1669000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1580000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1843000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1698000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1229000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>757000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1065000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>942000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2463000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2542000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2495000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45289</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E81" s="3">
         <v>189000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-63000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>202000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>281000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>432000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-61000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>203000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1262000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>75000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>143000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>478000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E83" s="3">
         <v>137000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>146000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>115000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>66000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>63000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>48000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>39000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>72000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>68000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>65000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>71000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>331000</v>
+      </c>
+      <c r="E89" s="3">
         <v>396000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>278000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>367000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>256000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>165000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>193000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>61000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>47000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>170000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>297000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>142000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>650000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-71000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-20000</v>
       </c>
       <c r="G91" s="3">
         <v>-20000</v>
       </c>
       <c r="H91" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-17000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-53000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-78000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-75000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-83000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E94" s="3">
         <v>37000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-428000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-877000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-158000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-491000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-981000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>101000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-44000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>52000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-88000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-66000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-61000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-54000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-46000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-44000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-45000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-47000</v>
       </c>
       <c r="L96" s="3">
         <v>-47000</v>
       </c>
       <c r="M96" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-36000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-37000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-30000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-359000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-399000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>87000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>225000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-133000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>654000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-290000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>584000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-192000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-210000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-148000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-116000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-377000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-15000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-28000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-43000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-52000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-34000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E102" s="3">
         <v>19000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-66000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-276000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-97000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-347000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-87000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-136000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>87000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>180000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KBR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KBR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>KBR</t>
   </si>
@@ -777,19 +777,19 @@
         <v>5736000</v>
       </c>
       <c r="F9" s="3">
-        <v>13066000</v>
+        <v>6533000</v>
       </c>
       <c r="G9" s="3">
-        <v>10202000</v>
+        <v>5101000</v>
       </c>
       <c r="H9" s="3">
         <v>4986000</v>
       </c>
       <c r="I9" s="3">
-        <v>8786000</v>
+        <v>4329000</v>
       </c>
       <c r="J9" s="3">
-        <v>7561000</v>
+        <v>3732000</v>
       </c>
       <c r="K9" s="3">
         <v>4156000</v>
@@ -822,19 +822,19 @@
         <v>828000</v>
       </c>
       <c r="F10" s="3">
-        <v>-5727000</v>
+        <v>806000</v>
       </c>
       <c r="G10" s="3">
-        <v>-4435000</v>
+        <v>666000</v>
       </c>
       <c r="H10" s="3">
         <v>653000</v>
       </c>
       <c r="I10" s="3">
-        <v>-3873000</v>
+        <v>584000</v>
       </c>
       <c r="J10" s="3">
-        <v>-3390000</v>
+        <v>439000</v>
       </c>
       <c r="K10" s="3">
         <v>112000</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>214000</v>
+        <v>645000</v>
       </c>
       <c r="E14" s="3">
-        <v>2000</v>
+        <v>-35000</v>
       </c>
       <c r="F14" s="3">
-        <v>14000</v>
+        <v>-6000</v>
       </c>
       <c r="G14" s="3">
-        <v>420000</v>
+        <v>304000</v>
       </c>
       <c r="H14" s="3">
-        <v>2000</v>
+        <v>-15000</v>
       </c>
       <c r="I14" s="3">
-        <v>-101000</v>
+        <v>-99000</v>
       </c>
       <c r="J14" s="3">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="K14" s="3">
         <v>39000</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>108000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6578000</v>
+        <v>6471000</v>
       </c>
       <c r="E17" s="3">
-        <v>6221000</v>
+        <v>6160000</v>
       </c>
       <c r="F17" s="3">
-        <v>7108000</v>
+        <v>6940000</v>
       </c>
       <c r="G17" s="3">
-        <v>5710000</v>
+        <v>5436000</v>
       </c>
       <c r="H17" s="3">
-        <v>5277000</v>
+        <v>5327000</v>
       </c>
       <c r="I17" s="3">
-        <v>4445000</v>
+        <v>4623000</v>
       </c>
       <c r="J17" s="3">
-        <v>3907000</v>
+        <v>3976000</v>
       </c>
       <c r="K17" s="3">
         <v>4240000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>378000</v>
+        <v>485000</v>
       </c>
       <c r="E18" s="3">
-        <v>343000</v>
+        <v>404000</v>
       </c>
       <c r="F18" s="3">
-        <v>231000</v>
+        <v>399000</v>
       </c>
       <c r="G18" s="3">
-        <v>57000</v>
+        <v>331000</v>
       </c>
       <c r="H18" s="3">
-        <v>362000</v>
+        <v>312000</v>
       </c>
       <c r="I18" s="3">
-        <v>468000</v>
+        <v>290000</v>
       </c>
       <c r="J18" s="3">
-        <v>264000</v>
+        <v>195000</v>
       </c>
       <c r="K18" s="3">
         <v>28000</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-147000</v>
+        <v>-109000</v>
       </c>
       <c r="E20" s="3">
-        <v>28000</v>
+        <v>68000</v>
       </c>
       <c r="F20" s="3">
-        <v>-5000</v>
+        <v>179000</v>
       </c>
       <c r="G20" s="3">
-        <v>1000</v>
+        <v>-31000</v>
       </c>
       <c r="H20" s="3">
-        <v>5000</v>
+        <v>-40000</v>
       </c>
       <c r="I20" s="3">
-        <v>-6000</v>
+        <v>-73000</v>
       </c>
       <c r="J20" s="3">
-        <v>4000</v>
+        <v>-74000</v>
       </c>
       <c r="K20" s="3">
         <v>5000</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>372000</v>
+        <v>689000</v>
       </c>
       <c r="E21" s="3">
-        <v>508000</v>
+        <v>426000</v>
       </c>
       <c r="F21" s="3">
-        <v>372000</v>
+        <v>328000</v>
       </c>
       <c r="G21" s="3">
-        <v>173000</v>
+        <v>440000</v>
       </c>
       <c r="H21" s="3">
-        <v>433000</v>
+        <v>418000</v>
       </c>
       <c r="I21" s="3">
-        <v>525000</v>
+        <v>426000</v>
       </c>
       <c r="J21" s="3">
-        <v>316000</v>
+        <v>317000</v>
       </c>
       <c r="K21" s="3">
         <v>78000</v>
@@ -1275,7 +1275,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>397000</v>
+        <v>115000</v>
       </c>
       <c r="E22" s="3">
         <v>87000</v>
@@ -1383,7 +1383,7 @@
         <v>86000</v>
       </c>
       <c r="J24" s="3">
-        <v>-29000</v>
+        <v>-193000</v>
       </c>
       <c r="K24" s="3">
         <v>84000</v>
@@ -1473,7 +1473,7 @@
         <v>310000</v>
       </c>
       <c r="J26" s="3">
-        <v>276000</v>
+        <v>440000</v>
       </c>
       <c r="K26" s="3">
         <v>-51000</v>
@@ -1512,13 +1512,13 @@
         <v>-63000</v>
       </c>
       <c r="H27" s="3">
-        <v>202000</v>
+        <v>200500</v>
       </c>
       <c r="I27" s="3">
-        <v>281000</v>
+        <v>279200</v>
       </c>
       <c r="J27" s="3">
-        <v>268000</v>
+        <v>429000</v>
       </c>
       <c r="K27" s="3">
         <v>-61000</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>164000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>147000</v>
+        <v>109000</v>
       </c>
       <c r="E32" s="3">
-        <v>-28000</v>
+        <v>-68000</v>
       </c>
       <c r="F32" s="3">
-        <v>5000</v>
+        <v>-179000</v>
       </c>
       <c r="G32" s="3">
-        <v>-1000</v>
+        <v>31000</v>
       </c>
       <c r="H32" s="3">
-        <v>-5000</v>
+        <v>40000</v>
       </c>
       <c r="I32" s="3">
-        <v>6000</v>
+        <v>73000</v>
       </c>
       <c r="J32" s="3">
-        <v>-4000</v>
+        <v>74000</v>
       </c>
       <c r="K32" s="3">
         <v>-5000</v>
@@ -1773,7 +1773,7 @@
         <v>-265000</v>
       </c>
       <c r="E33" s="3">
-        <v>189000</v>
+        <v>190000</v>
       </c>
       <c r="F33" s="3">
         <v>27000</v>
@@ -1863,7 +1863,7 @@
         <v>-265000</v>
       </c>
       <c r="E35" s="3">
-        <v>189000</v>
+        <v>190000</v>
       </c>
       <c r="F35" s="3">
         <v>27000</v>
@@ -2127,26 +2127,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>156000</v>
+        <v>73000</v>
       </c>
       <c r="E45" s="3">
-        <v>140000</v>
+        <v>73000</v>
       </c>
       <c r="F45" s="3">
-        <v>126000</v>
+        <v>51000</v>
       </c>
       <c r="G45" s="3">
-        <v>99000</v>
+        <v>28000</v>
       </c>
       <c r="H45" s="3">
-        <v>109000</v>
+        <v>44000</v>
       </c>
       <c r="I45" s="3">
-        <v>187000</v>
+        <v>30000</v>
       </c>
       <c r="J45" s="3">
-        <v>82000</v>
+        <v>29000</v>
       </c>
       <c r="K45" s="3">
         <v>103000</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>206000</v>
+        <v>224000</v>
       </c>
       <c r="E47" s="3">
         <v>217000</v>
       </c>
       <c r="F47" s="3">
-        <v>606000</v>
+        <v>583000</v>
       </c>
       <c r="G47" s="3">
-        <v>911000</v>
+        <v>881000</v>
       </c>
       <c r="H47" s="3">
-        <v>909000</v>
+        <v>846000</v>
       </c>
       <c r="I47" s="3">
-        <v>822000</v>
+        <v>724000</v>
       </c>
       <c r="J47" s="3">
-        <v>488000</v>
+        <v>387000</v>
       </c>
       <c r="K47" s="3">
         <v>500000</v>
@@ -2323,7 +2323,7 @@
         <v>305000</v>
       </c>
       <c r="I48" s="3">
-        <v>597000</v>
+        <v>121000</v>
       </c>
       <c r="J48" s="3">
         <v>130000</v>
@@ -2368,7 +2368,7 @@
         <v>1760000</v>
       </c>
       <c r="I49" s="3">
-        <v>2297000</v>
+        <v>1781000</v>
       </c>
       <c r="J49" s="3">
         <v>1207000</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>604000</v>
+        <v>347000</v>
       </c>
       <c r="E52" s="3">
-        <v>524000</v>
+        <v>311000</v>
       </c>
       <c r="F52" s="3">
-        <v>384000</v>
+        <v>176000</v>
       </c>
       <c r="G52" s="3">
-        <v>432000</v>
+        <v>135000</v>
       </c>
       <c r="H52" s="3">
-        <v>379000</v>
+        <v>143000</v>
       </c>
       <c r="I52" s="3">
-        <v>369000</v>
+        <v>147000</v>
       </c>
       <c r="J52" s="3">
-        <v>424000</v>
+        <v>124000</v>
       </c>
       <c r="K52" s="3">
         <v>245000</v>
@@ -2590,7 +2590,7 @@
         <v>5705000</v>
       </c>
       <c r="H54" s="3">
-        <v>5364000</v>
+        <v>5360000</v>
       </c>
       <c r="I54" s="3">
         <v>5052000</v>
@@ -2706,22 +2706,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>42000</v>
+        <v>90000</v>
       </c>
       <c r="E58" s="3">
-        <v>373000</v>
+        <v>412000</v>
       </c>
       <c r="F58" s="3">
-        <v>25000</v>
+        <v>67000</v>
       </c>
       <c r="G58" s="3">
-        <v>17000</v>
+        <v>76000</v>
       </c>
       <c r="H58" s="3">
-        <v>38000</v>
+        <v>85000</v>
       </c>
       <c r="I58" s="3">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="J58" s="3">
         <v>10000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>937000</v>
+        <v>508000</v>
       </c>
       <c r="E59" s="3">
-        <v>811000</v>
+        <v>415000</v>
       </c>
       <c r="F59" s="3">
-        <v>889000</v>
+        <v>431000</v>
       </c>
       <c r="G59" s="3">
-        <v>864000</v>
+        <v>493000</v>
       </c>
       <c r="H59" s="3">
-        <v>891000</v>
+        <v>599000</v>
       </c>
       <c r="I59" s="3">
-        <v>1028000</v>
+        <v>584000</v>
       </c>
       <c r="J59" s="3">
-        <v>711000</v>
+        <v>492000</v>
       </c>
       <c r="K59" s="3">
         <v>1015000</v>
@@ -2841,22 +2841,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1811000</v>
+        <v>1987000</v>
       </c>
       <c r="E61" s="3">
-        <v>1386000</v>
+        <v>1569000</v>
       </c>
       <c r="F61" s="3">
-        <v>1875000</v>
+        <v>2063000</v>
       </c>
       <c r="G61" s="3">
-        <v>1586000</v>
+        <v>1790000</v>
       </c>
       <c r="H61" s="3">
-        <v>1190000</v>
+        <v>1395000</v>
       </c>
       <c r="I61" s="3">
-        <v>1243000</v>
+        <v>1252000</v>
       </c>
       <c r="J61" s="3">
         <v>498000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>788000</v>
+        <v>506000</v>
       </c>
       <c r="E62" s="3">
-        <v>727000</v>
+        <v>452000</v>
       </c>
       <c r="F62" s="3">
-        <v>977000</v>
+        <v>425000</v>
       </c>
       <c r="G62" s="3">
-        <v>1055000</v>
+        <v>444000</v>
       </c>
       <c r="H62" s="3">
-        <v>816000</v>
+        <v>318000</v>
       </c>
       <c r="I62" s="3">
-        <v>672000</v>
+        <v>386000</v>
       </c>
       <c r="J62" s="3">
-        <v>884000</v>
+        <v>374000</v>
       </c>
       <c r="K62" s="3">
         <v>1156000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4182000</v>
+        <v>4171000</v>
       </c>
       <c r="E66" s="3">
-        <v>3946000</v>
+        <v>3934000</v>
       </c>
       <c r="F66" s="3">
-        <v>4535000</v>
+        <v>4521000</v>
       </c>
       <c r="G66" s="3">
-        <v>4125000</v>
+        <v>4096000</v>
       </c>
       <c r="H66" s="3">
-        <v>3521000</v>
+        <v>3507000</v>
       </c>
       <c r="I66" s="3">
-        <v>3354000</v>
+        <v>3334000</v>
       </c>
       <c r="J66" s="3">
-        <v>2445000</v>
+        <v>2453000</v>
       </c>
       <c r="K66" s="3">
         <v>3387000</v>
@@ -3322,7 +3322,7 @@
         <v>1305000</v>
       </c>
       <c r="H72" s="3">
-        <v>1441000</v>
+        <v>1437000</v>
       </c>
       <c r="I72" s="3">
         <v>1235000</v>
@@ -3502,7 +3502,7 @@
         <v>1580000</v>
       </c>
       <c r="H76" s="3">
-        <v>1843000</v>
+        <v>1839000</v>
       </c>
       <c r="I76" s="3">
         <v>1698000</v>
@@ -3633,7 +3633,7 @@
         <v>-265000</v>
       </c>
       <c r="E81" s="3">
-        <v>189000</v>
+        <v>190000</v>
       </c>
       <c r="F81" s="3">
         <v>27000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>141000</v>
+        <v>96000</v>
       </c>
       <c r="E83" s="3">
-        <v>137000</v>
+        <v>87000</v>
       </c>
       <c r="F83" s="3">
-        <v>146000</v>
+        <v>80000</v>
       </c>
       <c r="G83" s="3">
-        <v>115000</v>
+        <v>73000</v>
       </c>
       <c r="H83" s="3">
-        <v>66000</v>
+        <v>71000</v>
       </c>
       <c r="I83" s="3">
-        <v>63000</v>
+        <v>31000</v>
       </c>
       <c r="J83" s="3">
-        <v>48000</v>
+        <v>27000</v>
       </c>
       <c r="K83" s="3">
         <v>45000</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-72000</v>
+        <v>72000</v>
       </c>
       <c r="E96" s="3">
-        <v>-66000</v>
+        <v>66000</v>
       </c>
       <c r="F96" s="3">
-        <v>-61000</v>
+        <v>61000</v>
       </c>
       <c r="G96" s="3">
-        <v>-54000</v>
+        <v>54000</v>
       </c>
       <c r="H96" s="3">
-        <v>-46000</v>
+        <v>46000</v>
       </c>
       <c r="I96" s="3">
-        <v>-44000</v>
+        <v>44000</v>
       </c>
       <c r="J96" s="3">
-        <v>-45000</v>
+        <v>45000</v>
       </c>
       <c r="K96" s="3">
         <v>-46000</v>

--- a/AAII_Financials/Yearly/KBR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KBR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>KBR</t>
   </si>
@@ -656,207 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45660</v>
+      </c>
+      <c r="E7" s="2">
         <v>45289</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7742000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6956000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6564000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7339000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5767000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5639000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4913000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4171000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4268000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5096000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6366000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7214000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7770000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9103000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6639000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5979000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5736000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6533000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5101000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4986000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4329000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3732000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4156000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4771000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6431000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6797000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7252000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8463000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1103000</v>
+      </c>
+      <c r="E10" s="3">
         <v>977000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>828000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>806000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>666000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>653000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>584000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>439000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>112000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>325000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-65000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>417000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>518000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>640000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,81 +980,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E14" s="3">
         <v>645000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-35000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-6000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>304000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-15000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-99000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>39000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>70000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>660000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>360000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E15" s="3">
         <v>95000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>90000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>108000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>78000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>66000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>63000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>48000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7188000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6471000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6160000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6940000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5436000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5327000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4623000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3976000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4240000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4786000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7160000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6906000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7471000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8516000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>554000</v>
+      </c>
+      <c r="E18" s="3">
         <v>485000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>404000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>399000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>331000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>312000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>290000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>195000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>310000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-794000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>308000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>299000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>587000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,124 +1212,131 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-109000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>68000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>179000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-31000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-40000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-73000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-74000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>17000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>762000</v>
+      </c>
+      <c r="E21" s="3">
         <v>689000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>426000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>328000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>440000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>418000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>426000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>317000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>78000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>351000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-705000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>368000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>353000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>643000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E22" s="3">
         <v>115000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>87000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>80000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>72000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>99000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>66000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>21000</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
@@ -1313,99 +1353,108 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-166000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>284000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>146000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>268000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>396000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>247000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>312000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-777000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>300000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>288000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>572000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E24" s="3">
         <v>95000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>92000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>111000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>59000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>86000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-193000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>84000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>86000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>421000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>129000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>86000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>32000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>381000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-261000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>192000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-42000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>209000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>310000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>440000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-51000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>226000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1198000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>171000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>202000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>540000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-265000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>189000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-63000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>200500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>279200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>429000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-61000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>203000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1262000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>75000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>143000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>478000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,8 +1671,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1628,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E32" s="3">
         <v>109000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-68000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-179000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>31000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>40000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>73000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>74000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-17000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-265000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>190000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-63000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>202000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>281000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>432000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-61000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>203000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1262000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>75000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>143000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>478000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-265000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>190000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-63000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>202000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>281000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>432000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-61000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>203000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1262000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>75000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>143000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>478000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45660</v>
+      </c>
+      <c r="E38" s="2">
         <v>45289</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2073,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>350000</v>
+      </c>
+      <c r="E41" s="3">
         <v>304000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>389000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>370000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>436000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>712000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>739000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>439000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>536000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>883000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>970000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1106000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1053000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>966000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,54 +2166,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1380000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1191000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1218000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1656000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1099000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1190000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1141000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>904000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1408000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>861000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1364000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1543000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1790000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1654000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2148,252 +2244,270 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
         <v>5000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13000</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>73000</v>
+        <v>67000</v>
       </c>
       <c r="E45" s="3">
         <v>73000</v>
       </c>
       <c r="F45" s="3">
+        <v>73000</v>
+      </c>
+      <c r="G45" s="3">
         <v>51000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>44000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>103000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>204000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>202000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>523000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1065000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>815000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1873000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1651000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1747000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2152000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1634000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2011000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1959000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1425000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2047000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1844000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2454000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2925000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3444000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3435000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E47" s="3">
         <v>224000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>217000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>583000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>881000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>846000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>724000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>387000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>500000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>807000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>721000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>784000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>735000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>503000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E48" s="3">
         <v>377000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>346000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>294000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>284000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>305000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>121000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>130000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>145000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>690000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>247000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1227000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>390000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>384000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3393000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2727000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2732000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2768000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2444000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1760000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1781000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1207000</v>
       </c>
       <c r="K49" s="3">
         <v>1207000</v>
       </c>
       <c r="L49" s="3">
+        <v>1207000</v>
+      </c>
+      <c r="M49" s="3">
         <v>429000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>365000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>942000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>878000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E52" s="3">
         <v>347000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>311000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>176000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>135000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>143000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>147000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>124000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>245000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>233000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>291000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>457000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>320000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>280000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6663000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5565000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5566000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6204000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5705000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5360000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5052000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3674000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4144000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3412000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4078000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5438000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5767000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5666000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,82 +2785,86 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>777000</v>
+      </c>
+      <c r="E57" s="3">
         <v>593000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>637000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1026000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>574000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>572000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>546000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>350000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>535000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>438000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>742000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>747000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>756000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>761000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>90000</v>
+        <v>101000</v>
       </c>
       <c r="E58" s="3">
+        <v>79000</v>
+      </c>
+      <c r="F58" s="3">
         <v>412000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>67000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>76000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>85000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>35000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>10000</v>
       </c>
       <c r="M58" s="3">
         <v>10000</v>
@@ -2742,191 +2876,206 @@
         <v>10000</v>
       </c>
       <c r="P58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>11000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>508000</v>
+        <v>505000</v>
       </c>
       <c r="E59" s="3">
+        <v>519000</v>
+      </c>
+      <c r="F59" s="3">
         <v>415000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>431000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>493000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>599000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>584000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>492000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1015000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1227000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1226000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1559000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2112000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1506000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1782000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1572000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1821000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1875000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1455000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1501000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1419000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1071000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1559000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1393000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1978000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1907000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2184000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2277000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1987000</v>
+        <v>2770000</v>
       </c>
       <c r="E61" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1569000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2063000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1790000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1395000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1252000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>498000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>684000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>63000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>78000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>84000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>88000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>506000</v>
+        <v>561000</v>
       </c>
       <c r="E62" s="3">
+        <v>516000</v>
+      </c>
+      <c r="F62" s="3">
         <v>452000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>425000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>444000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>318000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>386000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>374000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1156000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>916000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1102000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1014000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1072000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>867000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5196000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4171000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3934000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4521000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4096000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3507000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3334000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2453000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3387000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2347000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3136000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2975000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3225000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3171000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1367000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1072000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1410000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1287000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1305000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1437000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1235000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>877000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>488000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2021000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1754000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1748000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1709000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1607000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1453000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1383000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1620000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1669000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1580000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1839000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1698000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1229000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>757000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1065000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>942000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2463000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2542000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2495000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45660</v>
+      </c>
+      <c r="E80" s="2">
         <v>45289</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-265000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>190000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-63000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>202000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>281000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>432000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-61000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>203000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1262000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>75000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>143000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>478000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E83" s="3">
         <v>96000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>87000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>80000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>73000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>71000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>27000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>72000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>68000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>65000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>71000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E89" s="3">
         <v>331000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>396000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>278000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>367000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>256000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>165000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>193000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>61000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>170000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>297000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>142000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>650000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-80000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-20000</v>
       </c>
       <c r="H91" s="3">
         <v>-20000</v>
       </c>
       <c r="I91" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-17000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-53000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-78000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-75000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-776000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-70000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>37000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-428000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-877000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-158000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-491000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-981000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>101000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-44000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>52000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-88000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4454,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E96" s="3">
         <v>72000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>66000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>61000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>54000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>46000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>44000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>45000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-47000</v>
       </c>
       <c r="M96" s="3">
         <v>-47000</v>
       </c>
       <c r="N96" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-36000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-37000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-359000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-399000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>87000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>225000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-133000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>654000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-290000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>584000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-192000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-210000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-148000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-116000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-377000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E101" s="3">
         <v>13000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-15000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-28000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-43000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-52000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-34000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>9000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-85000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-66000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-276000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-97000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-347000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-87000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-136000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>53000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>87000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>180000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KBR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KBR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>KBR</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46024</v>
+      </c>
+      <c r="E7" s="2">
         <v>45660</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45289</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7742000</v>
+        <v>7786000</v>
       </c>
       <c r="E8" s="3">
+        <v>7710000</v>
+      </c>
+      <c r="F8" s="3">
         <v>6956000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6564000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7339000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5767000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5639000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4913000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4171000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4268000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5096000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6366000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7214000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7770000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9103000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6639000</v>
+        <v>6636000</v>
       </c>
       <c r="E9" s="3">
+        <v>6611000</v>
+      </c>
+      <c r="F9" s="3">
         <v>5979000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5736000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6533000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5101000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4986000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4329000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3732000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4156000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4771000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6431000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6797000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7252000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8463000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1103000</v>
+        <v>1150000</v>
       </c>
       <c r="E10" s="3">
+        <v>1099000</v>
+      </c>
+      <c r="F10" s="3">
         <v>977000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>828000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>806000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>666000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>653000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>584000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>439000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>112000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>325000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-65000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>417000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>518000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>640000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,87 +999,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>645000</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>638000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-35000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-6000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>304000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-15000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-99000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>39000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>70000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>660000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>360000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E15" s="3">
         <v>108000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>95000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>90000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>108000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>78000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>66000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>63000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>48000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7188000</v>
+        <v>7218000</v>
       </c>
       <c r="E17" s="3">
-        <v>6471000</v>
+        <v>7158000</v>
       </c>
       <c r="F17" s="3">
+        <v>6477000</v>
+      </c>
+      <c r="G17" s="3">
         <v>6160000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6940000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5436000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5327000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4623000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3976000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4240000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4786000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7160000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6906000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7471000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8516000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>554000</v>
+        <v>568000</v>
       </c>
       <c r="E18" s="3">
-        <v>485000</v>
+        <v>552000</v>
       </c>
       <c r="F18" s="3">
+        <v>479000</v>
+      </c>
+      <c r="G18" s="3">
         <v>404000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>399000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>331000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>312000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>290000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>195000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>310000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-794000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>308000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>299000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>587000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,133 +1245,140 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-109000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>68000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>179000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-31000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-40000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-73000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-74000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>17000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-15000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>762000</v>
+        <v>889000</v>
       </c>
       <c r="E21" s="3">
-        <v>689000</v>
+        <v>760000</v>
       </c>
       <c r="F21" s="3">
+        <v>683000</v>
+      </c>
+      <c r="G21" s="3">
         <v>426000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>328000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>440000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>418000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>426000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>317000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>78000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>351000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-705000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>368000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>353000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>643000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E22" s="3">
         <v>144000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>115000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>87000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>80000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>72000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>99000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>66000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21000</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>511000</v>
+        <v>614000</v>
       </c>
       <c r="E23" s="3">
-        <v>-166000</v>
+        <v>508000</v>
       </c>
       <c r="F23" s="3">
+        <v>-165000</v>
+      </c>
+      <c r="G23" s="3">
         <v>284000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>146000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>268000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>396000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>247000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>312000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-777000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>300000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>288000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>572000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>130000</v>
+        <v>156000</v>
       </c>
       <c r="E24" s="3">
+        <v>129000</v>
+      </c>
+      <c r="F24" s="3">
         <v>95000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>92000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>111000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>59000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>86000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-193000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>84000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>86000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>421000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>129000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>86000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>32000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>381000</v>
+        <v>458000</v>
       </c>
       <c r="E26" s="3">
-        <v>-261000</v>
+        <v>379000</v>
       </c>
       <c r="F26" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="G26" s="3">
         <v>192000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>35000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-42000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>209000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>310000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>440000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-51000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>226000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1198000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>171000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>202000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>540000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>414000</v>
+      </c>
+      <c r="E27" s="3">
         <v>374000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-265000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>189000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-63000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>200500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>279200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>429000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-61000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>203000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1262000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>75000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>143000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>478000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,20 +1701,23 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E32" s="3">
         <v>100000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>109000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-68000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-179000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>31000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>40000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>73000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>74000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-17000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E33" s="3">
         <v>375000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-265000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>190000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-63000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>202000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>281000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>432000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-61000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>203000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1262000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>75000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>143000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>478000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E35" s="3">
         <v>375000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-265000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>190000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-63000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>202000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>281000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>432000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-61000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>203000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1262000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>75000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>143000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>478000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46024</v>
+      </c>
+      <c r="E38" s="2">
         <v>45660</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45289</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,61 +2159,65 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>350000</v>
+        <v>500000</v>
       </c>
       <c r="E41" s="3">
+        <v>342000</v>
+      </c>
+      <c r="F41" s="3">
         <v>304000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>389000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>370000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>436000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>712000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>739000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>439000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>536000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>883000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>970000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1106000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1053000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>966000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2169,57 +2258,63 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1380000</v>
+        <v>1409000</v>
       </c>
       <c r="E43" s="3">
+        <v>1373000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1191000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1218000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1656000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1099000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1190000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1141000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>904000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1408000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>861000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1364000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1543000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1790000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1654000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2247,267 +2342,285 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
         <v>5000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13000</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>67000</v>
+        <v>62000</v>
       </c>
       <c r="E45" s="3">
-        <v>73000</v>
+        <v>82000</v>
       </c>
       <c r="F45" s="3">
         <v>73000</v>
       </c>
       <c r="G45" s="3">
+        <v>73000</v>
+      </c>
+      <c r="H45" s="3">
         <v>51000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>103000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>204000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>202000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>523000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1065000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>815000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2051000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1873000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1651000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1747000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2152000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1634000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2011000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1959000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1425000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2047000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1844000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2454000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2925000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3444000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3435000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>210000</v>
+        <v>244000</v>
       </c>
       <c r="E47" s="3">
+        <v>336000</v>
+      </c>
+      <c r="F47" s="3">
         <v>224000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>217000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>583000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>881000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>846000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>724000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>387000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>500000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>807000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>721000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>784000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>735000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>503000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>492000</v>
+        <v>449000</v>
       </c>
       <c r="E48" s="3">
+        <v>440000</v>
+      </c>
+      <c r="F48" s="3">
         <v>377000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>346000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>294000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>284000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>305000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>121000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>130000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>145000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>690000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>247000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1227000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>390000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>384000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3404000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3393000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2727000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2732000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2768000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2444000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1760000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1781000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1207000</v>
       </c>
       <c r="L49" s="3">
         <v>1207000</v>
       </c>
       <c r="M49" s="3">
+        <v>1207000</v>
+      </c>
+      <c r="N49" s="3">
         <v>429000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>365000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>942000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>878000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1064000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>486000</v>
+        <v>274000</v>
       </c>
       <c r="E52" s="3">
+        <v>412000</v>
+      </c>
+      <c r="F52" s="3">
         <v>347000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>311000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>176000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>135000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>143000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>147000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>124000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>245000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>233000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>291000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>457000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>320000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>280000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6584000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6663000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5565000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5566000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6204000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5705000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5360000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5052000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3674000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4144000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3412000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4078000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5438000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5767000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5666000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,88 +2915,92 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>777000</v>
+        <v>712000</v>
       </c>
       <c r="E57" s="3">
+        <v>772000</v>
+      </c>
+      <c r="F57" s="3">
         <v>593000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>637000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1026000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>574000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>572000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>546000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>350000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>535000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>438000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>742000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>747000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>756000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>761000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>101000</v>
+        <v>111000</v>
       </c>
       <c r="E58" s="3">
+        <v>94000</v>
+      </c>
+      <c r="F58" s="3">
         <v>79000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>412000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>67000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>76000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>85000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>10000</v>
       </c>
       <c r="N58" s="3">
         <v>10000</v>
@@ -2879,203 +3012,218 @@
         <v>10000</v>
       </c>
       <c r="Q58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="R58" s="3">
         <v>11000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>505000</v>
+        <v>489000</v>
       </c>
       <c r="E59" s="3">
         <v>519000</v>
       </c>
       <c r="F59" s="3">
+        <v>519000</v>
+      </c>
+      <c r="G59" s="3">
         <v>415000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>431000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>493000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>599000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>584000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>492000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1015000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1227000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1226000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1559000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2112000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1506000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1688000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1782000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1572000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1821000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1875000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1455000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1501000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1419000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1071000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1559000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1393000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1978000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1907000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2184000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2277000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2770000</v>
+        <v>2788000</v>
       </c>
       <c r="E61" s="3">
+        <v>2761000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1977000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1569000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2063000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1790000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1395000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1252000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>498000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>684000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>63000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>78000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>84000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>88000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>561000</v>
+        <v>501000</v>
       </c>
       <c r="E62" s="3">
+        <v>570000</v>
+      </c>
+      <c r="F62" s="3">
         <v>516000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>452000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>425000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>444000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>318000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>386000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>374000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1156000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>916000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1102000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1014000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1072000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>867000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5072000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5196000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4171000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3934000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4521000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4096000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3507000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3334000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2453000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3387000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2347000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3136000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2975000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3225000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3171000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1697000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1367000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1072000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1410000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1287000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1305000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1437000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1235000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>877000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>488000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2021000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1754000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1748000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1709000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1607000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1503000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1453000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1383000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1620000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1669000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1580000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1839000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1698000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1229000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>757000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1065000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>942000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2463000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2542000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2495000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46024</v>
+      </c>
+      <c r="E80" s="2">
         <v>45660</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45289</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E81" s="3">
         <v>375000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-265000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>190000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-63000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>202000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>281000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>432000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-61000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>203000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1262000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>75000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>143000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>478000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E83" s="3">
         <v>104000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>96000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>87000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>80000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>73000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>71000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>31000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>27000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>39000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>72000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>68000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>65000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>71000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>524000</v>
+      </c>
+      <c r="E89" s="3">
         <v>462000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>331000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>396000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>278000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>367000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>256000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>165000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>193000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>61000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>47000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>170000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>297000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>142000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>650000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-77000</v>
+        <v>-42000</v>
       </c>
       <c r="E91" s="3">
-        <v>-80000</v>
+        <v>-52000</v>
       </c>
       <c r="F91" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-71000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-30000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-20000</v>
       </c>
       <c r="I91" s="3">
         <v>-20000</v>
       </c>
       <c r="J91" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-17000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-53000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-75000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-83000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-776000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-70000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>37000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-428000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-877000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-158000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-491000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-981000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>101000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-44000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-62000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>52000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-88000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E96" s="3">
         <v>79000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>72000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>66000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>61000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>54000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>46000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>44000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>45000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-47000</v>
       </c>
       <c r="N96" s="3">
         <v>-47000</v>
       </c>
       <c r="O96" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-36000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-30000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-391000</v>
+      </c>
+      <c r="E100" s="3">
         <v>374000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-359000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-399000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>87000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>225000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-133000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>654000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-290000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>584000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-192000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-210000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-148000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-116000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-377000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-14000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>13000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-15000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-28000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-43000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-52000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-34000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>9000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E102" s="3">
         <v>46000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-85000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-66000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-276000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>300000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-97000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-347000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-87000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-136000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>53000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>87000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>180000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
